--- a/Lab5/TestCase_Report_Bai5.xlsx
+++ b/Lab5/TestCase_Report_Bai5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ki2Nam4\Testing\Testing_Lab\Lab5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA204A2E-CCBC-4A32-838A-09D3B77BC78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208B27FF-239E-4389-891C-72FD5CBF178D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="306">
   <si>
     <t>SYSTEM TEST CASE</t>
   </si>
@@ -320,9 +320,6 @@
   </si>
   <si>
     <t>Hiện “Đăng ký tài khoản thành công!” và dữ liệu được lưu DB</t>
-  </si>
-  <si>
-    <t>TBD</t>
   </si>
   <si>
     <t>Kết hợp + kiểm tra DB</t>
@@ -2185,6 +2182,14 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2193,14 +2198,6 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10732,7 +10729,7 @@
       </c>
       <c r="I11" s="36">
         <f>User_Register!A6</f>
-        <v>0.90243902439024393</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -10778,7 +10775,7 @@
       </c>
       <c r="I12" s="41">
         <f>SUM(I11:I11)/COUNT(I11:I11)</f>
-        <v>0.90243902439024393</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -10905,7 +10902,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="45">
         <f>I12</f>
-        <v>0.90243902439024393</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -24016,13 +24013,13 @@
       <c r="A2" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="132" t="s">
+      <c r="B2" s="129" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="134"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="131"/>
       <c r="G2" s="69"/>
       <c r="H2" s="66"/>
       <c r="I2" s="66"/>
@@ -24051,7 +24048,7 @@
       <c r="A3" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="135"/>
+      <c r="B3" s="132"/>
       <c r="C3" s="105"/>
       <c r="D3" s="126"/>
       <c r="E3" s="105"/>
@@ -24084,7 +24081,7 @@
       <c r="A4" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="135"/>
+      <c r="B4" s="132"/>
       <c r="C4" s="105"/>
       <c r="D4" s="126"/>
       <c r="E4" s="105"/>
@@ -24159,7 +24156,7 @@
     <row r="6" spans="1:27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="76">
         <f>AVERAGE(L:L)</f>
-        <v>0.90243902439024393</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="B6" s="77">
         <f>COUNTIF(G12:G1002,"Pass")</f>
@@ -24311,21 +24308,21 @@
       <c r="M10" s="97"/>
     </row>
     <row r="11" spans="1:27" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A11" s="129" t="s">
+      <c r="A11" s="133" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="130"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="131"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="134"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="134"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="135"/>
     </row>
     <row r="12" spans="1:27" ht="118.8" x14ac:dyDescent="0.2">
       <c r="A12" s="84" t="s">
@@ -24335,10 +24332,10 @@
         <v>92</v>
       </c>
       <c r="C12" s="89" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="89" t="s">
         <v>104</v>
-      </c>
-      <c r="D12" s="89" t="s">
-        <v>105</v>
       </c>
       <c r="E12" s="88" t="s">
         <v>93</v>
@@ -24366,7 +24363,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="79.2" x14ac:dyDescent="0.2">
@@ -24374,19 +24371,19 @@
         <v>62</v>
       </c>
       <c r="B13" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="89" t="s">
+        <v>283</v>
+      </c>
+      <c r="D13" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="89" t="s">
-        <v>284</v>
-      </c>
-      <c r="D13" s="89" t="s">
+      <c r="E13" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="88" t="s">
-        <v>98</v>
-      </c>
       <c r="F13" s="88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G13" s="88" t="s">
         <v>24</v>
@@ -24408,7 +24405,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="39.6" x14ac:dyDescent="0.2">
@@ -24416,19 +24413,19 @@
         <v>63</v>
       </c>
       <c r="B14" s="88" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="89" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" s="89" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="89" t="s">
-        <v>283</v>
-      </c>
-      <c r="D14" s="89" t="s">
+      <c r="E14" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="88" t="s">
-        <v>102</v>
-      </c>
       <c r="F14" s="88" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G14" s="88" t="s">
         <v>24</v>
@@ -24450,44 +24447,44 @@
         <v>1</v>
       </c>
       <c r="M14" s="88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A15" s="129" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="130"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="130"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="131"/>
+      <c r="A15" s="133" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="134"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
+      <c r="L15" s="134"/>
+      <c r="M15" s="135"/>
     </row>
     <row r="16" spans="1:27" ht="66" x14ac:dyDescent="0.2">
       <c r="A16" s="84" t="s">
         <v>64</v>
       </c>
       <c r="B16" s="88" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="89" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="89" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="89" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" s="89" t="s">
+      <c r="E16" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="E16" s="88" t="s">
-        <v>109</v>
-      </c>
       <c r="F16" s="88" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G16" s="88" t="s">
         <v>24</v>
@@ -24509,7 +24506,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="13.2" x14ac:dyDescent="0.2">
@@ -24517,19 +24514,19 @@
         <v>65</v>
       </c>
       <c r="B17" s="88" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="89" t="s">
+      <c r="D17" s="89" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="89" t="s">
+      <c r="E17" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="E17" s="88" t="s">
-        <v>114</v>
-      </c>
       <c r="F17" s="88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G17" s="88" t="s">
         <v>24</v>
@@ -24551,7 +24548,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="39.6" x14ac:dyDescent="0.2">
@@ -24559,19 +24556,19 @@
         <v>66</v>
       </c>
       <c r="B18" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="89" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="89" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="89" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="89" t="s">
+      <c r="E18" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="88" t="s">
-        <v>118</v>
-      </c>
       <c r="F18" s="88" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G18" s="88" t="s">
         <v>24</v>
@@ -24593,7 +24590,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="85" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="13.2" x14ac:dyDescent="0.2">
@@ -24601,19 +24598,19 @@
         <v>67</v>
       </c>
       <c r="B19" s="88" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="D19" s="89" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="E19" s="88" t="s">
         <v>122</v>
       </c>
-      <c r="E19" s="88" t="s">
-        <v>123</v>
-      </c>
       <c r="F19" s="88" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G19" s="88" t="s">
         <v>24</v>
@@ -24635,7 +24632,7 @@
         <v>1</v>
       </c>
       <c r="M19" s="85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="13.2" x14ac:dyDescent="0.2">
@@ -24643,19 +24640,19 @@
         <v>68</v>
       </c>
       <c r="B20" s="88" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="89" t="s">
+      <c r="D20" s="89" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="89" t="s">
+      <c r="E20" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="88" t="s">
-        <v>128</v>
-      </c>
       <c r="F20" s="88" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G20" s="88" t="s">
         <v>24</v>
@@ -24677,7 +24674,7 @@
         <v>1</v>
       </c>
       <c r="M20" s="85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="13.2" x14ac:dyDescent="0.2">
@@ -24685,19 +24682,19 @@
         <v>69</v>
       </c>
       <c r="B21" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="C21" s="89" t="s">
+      <c r="D21" s="89" t="s">
         <v>131</v>
       </c>
-      <c r="D21" s="89" t="s">
+      <c r="E21" s="88" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="88" t="s">
-        <v>133</v>
-      </c>
       <c r="F21" s="88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G21" s="88" t="s">
         <v>24</v>
@@ -24719,7 +24716,7 @@
         <v>1</v>
       </c>
       <c r="M21" s="85" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="13.2" x14ac:dyDescent="0.2">
@@ -24727,19 +24724,19 @@
         <v>70</v>
       </c>
       <c r="B22" s="88" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="89" t="s">
         <v>135</v>
       </c>
-      <c r="C22" s="89" t="s">
+      <c r="D22" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="D22" s="89" t="s">
+      <c r="E22" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="E22" s="88" t="s">
-        <v>138</v>
-      </c>
       <c r="F22" s="88" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G22" s="88" t="s">
         <v>24</v>
@@ -24761,27 +24758,27 @@
         <v>1</v>
       </c>
       <c r="M22" s="85" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="105.6" x14ac:dyDescent="0.2">
       <c r="A23" s="89" t="s">
+        <v>284</v>
+      </c>
+      <c r="B23" s="88" t="s">
+        <v>290</v>
+      </c>
+      <c r="C23" s="89" t="s">
         <v>285</v>
       </c>
-      <c r="B23" s="88" t="s">
-        <v>291</v>
-      </c>
-      <c r="C23" s="89" t="s">
+      <c r="D23" s="89" t="s">
         <v>286</v>
       </c>
-      <c r="D23" s="89" t="s">
+      <c r="E23" s="88" t="s">
         <v>287</v>
       </c>
-      <c r="E23" s="88" t="s">
+      <c r="F23" s="88" t="s">
         <v>288</v>
-      </c>
-      <c r="F23" s="88" t="s">
-        <v>289</v>
       </c>
       <c r="G23" s="88" t="s">
         <v>25</v>
@@ -24803,44 +24800,44 @@
         <v>0</v>
       </c>
       <c r="M23" s="88" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A24" s="129" t="s">
-        <v>142</v>
-      </c>
-      <c r="B24" s="130"/>
-      <c r="C24" s="130"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
-      <c r="F24" s="130"/>
-      <c r="G24" s="130"/>
-      <c r="H24" s="130"/>
-      <c r="I24" s="130"/>
-      <c r="J24" s="130"/>
-      <c r="K24" s="130"/>
-      <c r="L24" s="130"/>
-      <c r="M24" s="131"/>
+      <c r="A24" s="133" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="134"/>
+      <c r="C24" s="134"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="134"/>
+      <c r="J24" s="134"/>
+      <c r="K24" s="134"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="135"/>
     </row>
     <row r="25" spans="1:13" ht="39.6" x14ac:dyDescent="0.2">
       <c r="A25" s="84" t="s">
         <v>71</v>
       </c>
       <c r="B25" s="88" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="89" t="s">
+        <v>168</v>
+      </c>
+      <c r="D25" s="89" t="s">
         <v>143</v>
       </c>
-      <c r="C25" s="89" t="s">
-        <v>169</v>
-      </c>
-      <c r="D25" s="89" t="s">
+      <c r="E25" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="E25" s="88" t="s">
-        <v>145</v>
-      </c>
       <c r="F25" s="88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G25" s="88" t="s">
         <v>24</v>
@@ -24862,7 +24859,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="13.2" x14ac:dyDescent="0.2">
@@ -24870,19 +24867,19 @@
         <v>72</v>
       </c>
       <c r="B26" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="89" t="s">
         <v>146</v>
       </c>
-      <c r="C26" s="89" t="s">
+      <c r="D26" s="89" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="89" t="s">
+      <c r="E26" s="88" t="s">
         <v>148</v>
       </c>
-      <c r="E26" s="88" t="s">
-        <v>149</v>
-      </c>
       <c r="F26" s="88" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G26" s="88" t="s">
         <v>24</v>
@@ -24904,7 +24901,7 @@
         <v>1</v>
       </c>
       <c r="M26" s="85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="13.2" x14ac:dyDescent="0.2">
@@ -24912,19 +24909,19 @@
         <v>73</v>
       </c>
       <c r="B27" s="88" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="C27" s="89" t="s">
+      <c r="D27" s="89" t="s">
         <v>152</v>
       </c>
-      <c r="D27" s="89" t="s">
+      <c r="E27" s="88" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="88" t="s">
-        <v>154</v>
-      </c>
       <c r="F27" s="88" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G27" s="88" t="s">
         <v>24</v>
@@ -24946,7 +24943,7 @@
         <v>1</v>
       </c>
       <c r="M27" s="85" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="13.2" x14ac:dyDescent="0.2">
@@ -24954,19 +24951,19 @@
         <v>74</v>
       </c>
       <c r="B28" s="88" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="89" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="89" t="s">
+      <c r="D28" s="89" t="s">
         <v>157</v>
       </c>
-      <c r="D28" s="89" t="s">
+      <c r="E28" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="E28" s="88" t="s">
-        <v>159</v>
-      </c>
       <c r="F28" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G28" s="88" t="s">
         <v>24</v>
@@ -24988,7 +24985,7 @@
         <v>1</v>
       </c>
       <c r="M28" s="85" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -24996,19 +24993,19 @@
         <v>75</v>
       </c>
       <c r="B29" s="88" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="89" t="s">
         <v>161</v>
       </c>
-      <c r="C29" s="89" t="s">
+      <c r="D29" s="89" t="s">
         <v>162</v>
       </c>
-      <c r="D29" s="89" t="s">
-        <v>163</v>
-      </c>
       <c r="E29" s="88" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F29" s="88" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G29" s="88" t="s">
         <v>24</v>
@@ -25030,7 +25027,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25038,19 +25035,19 @@
         <v>76</v>
       </c>
       <c r="B30" s="88" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" s="89" t="s">
         <v>165</v>
       </c>
-      <c r="C30" s="89" t="s">
+      <c r="D30" s="89" t="s">
         <v>166</v>
       </c>
-      <c r="D30" s="89" t="s">
-        <v>167</v>
-      </c>
       <c r="E30" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F30" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G30" s="88" t="s">
         <v>24</v>
@@ -25072,44 +25069,44 @@
         <v>1</v>
       </c>
       <c r="M30" s="85" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="129" t="s">
-        <v>170</v>
-      </c>
-      <c r="B31" s="130"/>
-      <c r="C31" s="130"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="130"/>
-      <c r="F31" s="130"/>
-      <c r="G31" s="130"/>
-      <c r="H31" s="130"/>
-      <c r="I31" s="130"/>
-      <c r="J31" s="130"/>
-      <c r="K31" s="130"/>
-      <c r="L31" s="130"/>
-      <c r="M31" s="131"/>
+      <c r="A31" s="133" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31" s="134"/>
+      <c r="C31" s="134"/>
+      <c r="D31" s="134"/>
+      <c r="E31" s="134"/>
+      <c r="F31" s="134"/>
+      <c r="G31" s="134"/>
+      <c r="H31" s="134"/>
+      <c r="I31" s="134"/>
+      <c r="J31" s="134"/>
+      <c r="K31" s="134"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="135"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="84" t="s">
         <v>77</v>
       </c>
       <c r="B32" s="88" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" s="89" t="s">
         <v>171</v>
       </c>
-      <c r="C32" s="89" t="s">
+      <c r="D32" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="D32" s="89" t="s">
-        <v>173</v>
-      </c>
       <c r="E32" s="88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F32" s="88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G32" s="88" t="s">
         <v>24</v>
@@ -25131,7 +25128,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25139,19 +25136,19 @@
         <v>78</v>
       </c>
       <c r="B33" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="C33" s="89" t="s">
+      <c r="D33" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="D33" s="89" t="s">
+      <c r="E33" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="E33" s="88" t="s">
-        <v>177</v>
-      </c>
       <c r="F33" s="88" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G33" s="88" t="s">
         <v>24</v>
@@ -25173,7 +25170,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25181,19 +25178,19 @@
         <v>79</v>
       </c>
       <c r="B34" s="88" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="89" t="s">
         <v>178</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="D34" s="89" t="s">
         <v>179</v>
       </c>
-      <c r="D34" s="89" t="s">
+      <c r="E34" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="E34" s="88" t="s">
-        <v>181</v>
-      </c>
       <c r="F34" s="88" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G34" s="88" t="s">
         <v>24</v>
@@ -25215,7 +25212,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25223,19 +25220,19 @@
         <v>80</v>
       </c>
       <c r="B35" s="88" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" s="89" t="s">
         <v>182</v>
       </c>
-      <c r="C35" s="89" t="s">
+      <c r="D35" s="89" t="s">
         <v>183</v>
       </c>
-      <c r="D35" s="89" t="s">
-        <v>184</v>
-      </c>
       <c r="E35" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F35" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G35" s="88" t="s">
         <v>24</v>
@@ -25257,7 +25254,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="85" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25265,19 +25262,19 @@
         <v>81</v>
       </c>
       <c r="B36" s="88" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" s="89" t="s">
         <v>185</v>
       </c>
-      <c r="C36" s="89" t="s">
+      <c r="D36" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="D36" s="89" t="s">
+      <c r="E36" s="88" t="s">
         <v>187</v>
       </c>
-      <c r="E36" s="88" t="s">
-        <v>188</v>
-      </c>
       <c r="F36" s="88" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G36" s="88" t="s">
         <v>24</v>
@@ -25299,27 +25296,27 @@
         <v>1</v>
       </c>
       <c r="M36" s="85" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="66" x14ac:dyDescent="0.2">
       <c r="A37" s="89" t="s">
+        <v>302</v>
+      </c>
+      <c r="B37" s="88" t="s">
         <v>303</v>
       </c>
-      <c r="B37" s="88" t="s">
+      <c r="C37" s="89" t="s">
         <v>304</v>
       </c>
-      <c r="C37" s="89" t="s">
+      <c r="D37" s="89" t="s">
         <v>305</v>
       </c>
-      <c r="D37" s="89" t="s">
-        <v>306</v>
-      </c>
       <c r="E37" s="88" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F37" s="88" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G37" s="88" t="s">
         <v>25</v>
@@ -25341,44 +25338,44 @@
         <v>0</v>
       </c>
       <c r="M37" s="88" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="129" t="s">
-        <v>189</v>
-      </c>
-      <c r="B38" s="130"/>
-      <c r="C38" s="130"/>
-      <c r="D38" s="130"/>
-      <c r="E38" s="130"/>
-      <c r="F38" s="130"/>
-      <c r="G38" s="130"/>
-      <c r="H38" s="130"/>
-      <c r="I38" s="130"/>
-      <c r="J38" s="130"/>
-      <c r="K38" s="130"/>
-      <c r="L38" s="130"/>
-      <c r="M38" s="131"/>
+      <c r="A38" s="133" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" s="134"/>
+      <c r="C38" s="134"/>
+      <c r="D38" s="134"/>
+      <c r="E38" s="134"/>
+      <c r="F38" s="134"/>
+      <c r="G38" s="134"/>
+      <c r="H38" s="134"/>
+      <c r="I38" s="134"/>
+      <c r="J38" s="134"/>
+      <c r="K38" s="134"/>
+      <c r="L38" s="134"/>
+      <c r="M38" s="135"/>
     </row>
     <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="84" t="s">
         <v>82</v>
       </c>
       <c r="B39" s="88" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" s="89" t="s">
         <v>190</v>
       </c>
-      <c r="C39" s="89" t="s">
+      <c r="D39" s="89" t="s">
         <v>191</v>
       </c>
-      <c r="D39" s="89" t="s">
-        <v>192</v>
-      </c>
       <c r="E39" s="88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G39" s="88" t="s">
         <v>24</v>
@@ -25400,7 +25397,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25408,19 +25405,19 @@
         <v>83</v>
       </c>
       <c r="B40" s="88" t="s">
+        <v>192</v>
+      </c>
+      <c r="C40" s="89" t="s">
         <v>193</v>
       </c>
-      <c r="C40" s="89" t="s">
+      <c r="D40" s="89" t="s">
         <v>194</v>
       </c>
-      <c r="D40" s="89" t="s">
+      <c r="E40" s="88" t="s">
         <v>195</v>
       </c>
-      <c r="E40" s="88" t="s">
-        <v>196</v>
-      </c>
       <c r="F40" s="88" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G40" s="88" t="s">
         <v>24</v>
@@ -25442,7 +25439,7 @@
         <v>1</v>
       </c>
       <c r="M40" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25450,19 +25447,19 @@
         <v>84</v>
       </c>
       <c r="B41" s="88" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="89" t="s">
         <v>197</v>
       </c>
-      <c r="C41" s="89" t="s">
+      <c r="D41" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="D41" s="89" t="s">
+      <c r="E41" s="88" t="s">
         <v>199</v>
       </c>
-      <c r="E41" s="88" t="s">
-        <v>200</v>
-      </c>
       <c r="F41" s="88" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G41" s="88" t="s">
         <v>24</v>
@@ -25484,7 +25481,7 @@
         <v>1</v>
       </c>
       <c r="M41" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25492,19 +25489,19 @@
         <v>85</v>
       </c>
       <c r="B42" s="88" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" s="89" t="s">
         <v>201</v>
       </c>
-      <c r="C42" s="89" t="s">
+      <c r="D42" s="89" t="s">
         <v>202</v>
       </c>
-      <c r="D42" s="89" t="s">
+      <c r="E42" s="88" t="s">
         <v>203</v>
       </c>
-      <c r="E42" s="88" t="s">
-        <v>204</v>
-      </c>
       <c r="F42" s="88" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G42" s="88" t="s">
         <v>24</v>
@@ -25526,27 +25523,27 @@
         <v>1</v>
       </c>
       <c r="M42" s="85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="84" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="B43" s="88" t="s">
+      <c r="C43" s="89" t="s">
         <v>206</v>
       </c>
-      <c r="C43" s="89" t="s">
+      <c r="D43" s="89" t="s">
         <v>207</v>
       </c>
-      <c r="D43" s="89" t="s">
-        <v>208</v>
-      </c>
       <c r="E43" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F43" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G43" s="88" t="s">
         <v>24</v>
@@ -25568,27 +25565,27 @@
         <v>1</v>
       </c>
       <c r="M43" s="85" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="84" t="s">
+        <v>208</v>
+      </c>
+      <c r="B44" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="B44" s="88" t="s">
+      <c r="C44" s="89" t="s">
         <v>210</v>
       </c>
-      <c r="C44" s="89" t="s">
+      <c r="D44" s="89" t="s">
         <v>211</v>
       </c>
-      <c r="D44" s="89" t="s">
-        <v>212</v>
-      </c>
       <c r="E44" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F44" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G44" s="88" t="s">
         <v>24</v>
@@ -25610,27 +25607,27 @@
         <v>1</v>
       </c>
       <c r="M44" s="85" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="84" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" s="88" t="s">
         <v>213</v>
       </c>
-      <c r="B45" s="88" t="s">
+      <c r="C45" s="89" t="s">
         <v>214</v>
       </c>
-      <c r="C45" s="89" t="s">
+      <c r="D45" s="89" t="s">
         <v>215</v>
       </c>
-      <c r="D45" s="89" t="s">
-        <v>216</v>
-      </c>
       <c r="E45" s="88" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F45" s="88" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G45" s="88" t="s">
         <v>24</v>
@@ -25652,44 +25649,44 @@
         <v>1</v>
       </c>
       <c r="M45" s="85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="129" t="s">
-        <v>217</v>
-      </c>
-      <c r="B46" s="130"/>
-      <c r="C46" s="130"/>
-      <c r="D46" s="130"/>
-      <c r="E46" s="130"/>
-      <c r="F46" s="130"/>
-      <c r="G46" s="130"/>
-      <c r="H46" s="130"/>
-      <c r="I46" s="130"/>
-      <c r="J46" s="130"/>
-      <c r="K46" s="130"/>
-      <c r="L46" s="130"/>
-      <c r="M46" s="131"/>
+      <c r="A46" s="133" t="s">
+        <v>216</v>
+      </c>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
+      <c r="D46" s="134"/>
+      <c r="E46" s="134"/>
+      <c r="F46" s="134"/>
+      <c r="G46" s="134"/>
+      <c r="H46" s="134"/>
+      <c r="I46" s="134"/>
+      <c r="J46" s="134"/>
+      <c r="K46" s="134"/>
+      <c r="L46" s="134"/>
+      <c r="M46" s="135"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="84" t="s">
+        <v>217</v>
+      </c>
+      <c r="B47" s="88" t="s">
         <v>218</v>
       </c>
-      <c r="B47" s="88" t="s">
+      <c r="C47" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="C47" s="89" t="s">
+      <c r="D47" s="89" t="s">
         <v>220</v>
       </c>
-      <c r="D47" s="89" t="s">
-        <v>221</v>
-      </c>
       <c r="E47" s="88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F47" s="88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G47" s="88" t="s">
         <v>24</v>
@@ -25711,27 +25708,27 @@
         <v>1</v>
       </c>
       <c r="M47" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="84" t="s">
+        <v>221</v>
+      </c>
+      <c r="B48" s="88" t="s">
         <v>222</v>
       </c>
-      <c r="B48" s="88" t="s">
+      <c r="C48" s="89" t="s">
         <v>223</v>
       </c>
-      <c r="C48" s="89" t="s">
+      <c r="D48" s="89" t="s">
         <v>224</v>
       </c>
-      <c r="D48" s="89" t="s">
-        <v>225</v>
-      </c>
       <c r="E48" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F48" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G48" s="88" t="s">
         <v>24</v>
@@ -25753,27 +25750,27 @@
         <v>1</v>
       </c>
       <c r="M48" s="85" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="84" t="s">
+        <v>225</v>
+      </c>
+      <c r="B49" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="B49" s="88" t="s">
+      <c r="C49" s="89" t="s">
         <v>227</v>
       </c>
-      <c r="C49" s="89" t="s">
+      <c r="D49" s="89" t="s">
         <v>228</v>
       </c>
-      <c r="D49" s="89" t="s">
+      <c r="E49" s="88" t="s">
         <v>229</v>
       </c>
-      <c r="E49" s="88" t="s">
-        <v>230</v>
-      </c>
       <c r="F49" s="88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G49" s="88" t="s">
         <v>24</v>
@@ -25795,44 +25792,44 @@
         <v>1</v>
       </c>
       <c r="M49" s="85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="129" t="s">
-        <v>231</v>
-      </c>
-      <c r="B50" s="130"/>
-      <c r="C50" s="130"/>
-      <c r="D50" s="130"/>
-      <c r="E50" s="130"/>
-      <c r="F50" s="130"/>
-      <c r="G50" s="130"/>
-      <c r="H50" s="130"/>
-      <c r="I50" s="130"/>
-      <c r="J50" s="130"/>
-      <c r="K50" s="130"/>
-      <c r="L50" s="130"/>
-      <c r="M50" s="131"/>
+      <c r="A50" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="B50" s="134"/>
+      <c r="C50" s="134"/>
+      <c r="D50" s="134"/>
+      <c r="E50" s="134"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="134"/>
+      <c r="H50" s="134"/>
+      <c r="I50" s="134"/>
+      <c r="J50" s="134"/>
+      <c r="K50" s="134"/>
+      <c r="L50" s="134"/>
+      <c r="M50" s="135"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="84" t="s">
+        <v>231</v>
+      </c>
+      <c r="B51" s="88" t="s">
         <v>232</v>
       </c>
-      <c r="B51" s="88" t="s">
+      <c r="C51" s="89" t="s">
         <v>233</v>
       </c>
-      <c r="C51" s="89" t="s">
+      <c r="D51" s="89" t="s">
         <v>234</v>
       </c>
-      <c r="D51" s="89" t="s">
+      <c r="E51" s="88" t="s">
         <v>235</v>
       </c>
-      <c r="E51" s="88" t="s">
-        <v>236</v>
-      </c>
       <c r="F51" s="88" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G51" s="88" t="s">
         <v>24</v>
@@ -25854,27 +25851,27 @@
         <v>1</v>
       </c>
       <c r="M51" s="85" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="84" t="s">
+        <v>237</v>
+      </c>
+      <c r="B52" s="88" t="s">
         <v>238</v>
       </c>
-      <c r="B52" s="88" t="s">
+      <c r="C52" s="89" t="s">
         <v>239</v>
       </c>
-      <c r="C52" s="89" t="s">
+      <c r="D52" s="89" t="s">
         <v>240</v>
       </c>
-      <c r="D52" s="89" t="s">
+      <c r="E52" s="88" t="s">
         <v>241</v>
       </c>
-      <c r="E52" s="88" t="s">
-        <v>242</v>
-      </c>
       <c r="F52" s="88" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G52" s="88" t="s">
         <v>24</v>
@@ -25896,27 +25893,27 @@
         <v>1</v>
       </c>
       <c r="M52" s="85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="84" t="s">
+        <v>242</v>
+      </c>
+      <c r="B53" s="88" t="s">
         <v>243</v>
       </c>
-      <c r="B53" s="88" t="s">
+      <c r="C53" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="C53" s="89" t="s">
+      <c r="D53" s="89" t="s">
         <v>245</v>
       </c>
-      <c r="D53" s="89" t="s">
-        <v>246</v>
-      </c>
       <c r="E53" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F53" s="88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G53" s="88" t="s">
         <v>24</v>
@@ -25938,27 +25935,27 @@
         <v>1</v>
       </c>
       <c r="M53" s="85" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="84" t="s">
+        <v>246</v>
+      </c>
+      <c r="B54" s="88" t="s">
         <v>247</v>
       </c>
-      <c r="B54" s="88" t="s">
+      <c r="C54" s="89" t="s">
         <v>248</v>
       </c>
-      <c r="C54" s="89" t="s">
+      <c r="D54" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D54" s="89" t="s">
+      <c r="E54" s="88" t="s">
         <v>250</v>
       </c>
-      <c r="E54" s="88" t="s">
-        <v>251</v>
-      </c>
       <c r="F54" s="88" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G54" s="88" t="s">
         <v>24</v>
@@ -25980,27 +25977,27 @@
         <v>1</v>
       </c>
       <c r="M54" s="85" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="89" t="s">
+        <v>252</v>
+      </c>
+      <c r="B55" s="88" t="s">
         <v>253</v>
       </c>
-      <c r="B55" s="88" t="s">
+      <c r="C55" s="89" t="s">
         <v>254</v>
       </c>
-      <c r="C55" s="89" t="s">
+      <c r="D55" s="89" t="s">
         <v>255</v>
       </c>
-      <c r="D55" s="89" t="s">
+      <c r="E55" s="88" t="s">
         <v>256</v>
       </c>
-      <c r="E55" s="88" t="s">
-        <v>257</v>
-      </c>
       <c r="F55" s="88" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G55" s="88" t="s">
         <v>24</v>
@@ -26022,27 +26019,27 @@
         <v>1</v>
       </c>
       <c r="M55" s="85" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="89" t="s">
+        <v>291</v>
+      </c>
+      <c r="B56" s="88" t="s">
         <v>292</v>
       </c>
-      <c r="B56" s="88" t="s">
+      <c r="C56" s="89" t="s">
         <v>293</v>
       </c>
-      <c r="C56" s="89" t="s">
+      <c r="D56" s="89" t="s">
         <v>294</v>
       </c>
-      <c r="D56" s="89" t="s">
+      <c r="E56" s="88" t="s">
+        <v>287</v>
+      </c>
+      <c r="F56" s="88" t="s">
         <v>295</v>
-      </c>
-      <c r="E56" s="88" t="s">
-        <v>288</v>
-      </c>
-      <c r="F56" s="88" t="s">
-        <v>296</v>
       </c>
       <c r="G56" s="88" t="s">
         <v>25</v>
@@ -26064,44 +26061,44 @@
         <v>0</v>
       </c>
       <c r="M56" s="88" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="129" t="s">
-        <v>258</v>
-      </c>
-      <c r="B57" s="130"/>
-      <c r="C57" s="130"/>
-      <c r="D57" s="130"/>
-      <c r="E57" s="130"/>
-      <c r="F57" s="130"/>
-      <c r="G57" s="130"/>
-      <c r="H57" s="130"/>
-      <c r="I57" s="130"/>
-      <c r="J57" s="130"/>
-      <c r="K57" s="130"/>
-      <c r="L57" s="130"/>
-      <c r="M57" s="131"/>
+      <c r="A57" s="133" t="s">
+        <v>257</v>
+      </c>
+      <c r="B57" s="134"/>
+      <c r="C57" s="134"/>
+      <c r="D57" s="134"/>
+      <c r="E57" s="134"/>
+      <c r="F57" s="134"/>
+      <c r="G57" s="134"/>
+      <c r="H57" s="134"/>
+      <c r="I57" s="134"/>
+      <c r="J57" s="134"/>
+      <c r="K57" s="134"/>
+      <c r="L57" s="134"/>
+      <c r="M57" s="135"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="89" t="s">
+        <v>297</v>
+      </c>
+      <c r="B58" s="88" t="s">
         <v>298</v>
       </c>
-      <c r="B58" s="88" t="s">
+      <c r="C58" s="89" t="s">
         <v>299</v>
       </c>
-      <c r="C58" s="89" t="s">
+      <c r="D58" s="89" t="s">
         <v>300</v>
       </c>
-      <c r="D58" s="89" t="s">
+      <c r="E58" s="88" t="s">
+        <v>287</v>
+      </c>
+      <c r="F58" s="88" t="s">
         <v>301</v>
-      </c>
-      <c r="E58" s="88" t="s">
-        <v>288</v>
-      </c>
-      <c r="F58" s="88" t="s">
-        <v>302</v>
       </c>
       <c r="G58" s="88" t="s">
         <v>25</v>
@@ -26123,27 +26120,27 @@
         <v>1</v>
       </c>
       <c r="M58" s="85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="84" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B59" s="88" t="s">
+        <v>258</v>
+      </c>
+      <c r="C59" s="89" t="s">
         <v>259</v>
       </c>
-      <c r="C59" s="89" t="s">
+      <c r="D59" s="89" t="s">
         <v>260</v>
       </c>
-      <c r="D59" s="89" t="s">
+      <c r="E59" s="88" t="s">
         <v>261</v>
       </c>
-      <c r="E59" s="88" t="s">
-        <v>262</v>
-      </c>
       <c r="F59" s="88" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G59" s="88" t="s">
         <v>24</v>
@@ -26165,44 +26162,44 @@
         <v>0</v>
       </c>
       <c r="M59" s="85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="129" t="s">
-        <v>265</v>
-      </c>
-      <c r="B60" s="130"/>
-      <c r="C60" s="130"/>
-      <c r="D60" s="130"/>
-      <c r="E60" s="130"/>
-      <c r="F60" s="130"/>
-      <c r="G60" s="130"/>
-      <c r="H60" s="130"/>
-      <c r="I60" s="130"/>
-      <c r="J60" s="130"/>
-      <c r="K60" s="130"/>
-      <c r="L60" s="130"/>
-      <c r="M60" s="131"/>
+      <c r="A60" s="133" t="s">
+        <v>264</v>
+      </c>
+      <c r="B60" s="134"/>
+      <c r="C60" s="134"/>
+      <c r="D60" s="134"/>
+      <c r="E60" s="134"/>
+      <c r="F60" s="134"/>
+      <c r="G60" s="134"/>
+      <c r="H60" s="134"/>
+      <c r="I60" s="134"/>
+      <c r="J60" s="134"/>
+      <c r="K60" s="134"/>
+      <c r="L60" s="134"/>
+      <c r="M60" s="135"/>
     </row>
     <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="89" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B61" s="88" t="s">
+        <v>265</v>
+      </c>
+      <c r="C61" s="89" t="s">
         <v>266</v>
       </c>
-      <c r="C61" s="89" t="s">
+      <c r="D61" s="89" t="s">
         <v>267</v>
       </c>
-      <c r="D61" s="89" t="s">
+      <c r="E61" s="88" t="s">
         <v>268</v>
       </c>
-      <c r="E61" s="88" t="s">
-        <v>269</v>
-      </c>
       <c r="F61" s="88" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G61" s="88" t="s">
         <v>24</v>
@@ -26219,31 +26216,32 @@
       <c r="K61" s="85">
         <v>1</v>
       </c>
-      <c r="L61" s="86" t="s">
-        <v>94</v>
+      <c r="L61" s="86">
+        <f>K61/J61</f>
+        <v>1</v>
       </c>
       <c r="M61" s="85" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="89" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B62" s="88" t="s">
+        <v>270</v>
+      </c>
+      <c r="C62" s="89" t="s">
         <v>271</v>
       </c>
-      <c r="C62" s="89" t="s">
+      <c r="D62" s="89" t="s">
         <v>272</v>
       </c>
-      <c r="D62" s="89" t="s">
+      <c r="E62" s="88" t="s">
         <v>273</v>
       </c>
-      <c r="E62" s="88" t="s">
-        <v>274</v>
-      </c>
       <c r="F62" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G62" s="88" t="s">
         <v>24</v>
@@ -26260,31 +26258,32 @@
       <c r="K62" s="85">
         <v>1</v>
       </c>
-      <c r="L62" s="86" t="s">
-        <v>94</v>
+      <c r="L62" s="86">
+        <f>K62/J62</f>
+        <v>1</v>
       </c>
       <c r="M62" s="85" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="89" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B63" s="88" t="s">
+        <v>274</v>
+      </c>
+      <c r="C63" s="89" t="s">
         <v>275</v>
       </c>
-      <c r="C63" s="89" t="s">
+      <c r="D63" s="89" t="s">
         <v>276</v>
       </c>
-      <c r="D63" s="89" t="s">
+      <c r="E63" s="88" t="s">
         <v>277</v>
       </c>
-      <c r="E63" s="88" t="s">
-        <v>278</v>
-      </c>
       <c r="F63" s="88" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G63" s="88" t="s">
         <v>24</v>
@@ -26301,11 +26300,12 @@
       <c r="K63" s="85">
         <v>1</v>
       </c>
-      <c r="L63" s="86" t="s">
-        <v>94</v>
+      <c r="L63" s="86">
+        <f>K63/J63</f>
+        <v>1</v>
       </c>
       <c r="M63" s="85" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -27594,11 +27594,6 @@
     <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A15:M15"/>
     <mergeCell ref="A57:M57"/>
     <mergeCell ref="A60:M60"/>
     <mergeCell ref="A24:M24"/>
@@ -27606,6 +27601,11 @@
     <mergeCell ref="A38:M38"/>
     <mergeCell ref="A46:M46"/>
     <mergeCell ref="A50:M50"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A15:M15"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G9:G10" xr:uid="{00000000-0002-0000-0300-000000000000}">
